--- a/data/matches/leagues/Sweden_Allsvenskan_2026.xlsx
+++ b/data/matches/leagues/Sweden_Allsvenskan_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EH6" headerRowCount="1">
-  <autoFilter ref="A1:EH6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EH9" headerRowCount="1">
+  <autoFilter ref="A1:EH9"/>
   <tableColumns count="138">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -576,14 +576,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EH6"/>
+  <dimension ref="A1:EH9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="9.6" customWidth="1" min="2" max="2"/>
     <col width="13.2" customWidth="1" min="3" max="3"/>
     <col width="13.2" customWidth="1" min="4" max="4"/>
-    <col width="15.6" customWidth="1" min="5" max="5"/>
+    <col width="19.2" customWidth="1" min="5" max="5"/>
     <col width="25.2" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
@@ -2365,10 +2365,10 @@
         <v>20</v>
       </c>
       <c r="Y4" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Z4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>-1</v>
+        <v>6789</v>
       </c>
       <c r="BG4" t="n">
         <v>2</v>
@@ -2912,7 +2912,7 @@
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-1</v>
+        <v>39085</v>
       </c>
       <c r="BG5" t="n">
         <v>2</v>
@@ -3243,13 +3243,13 @@
         <v>6</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T6" t="n">
         <v>13</v>
       </c>
       <c r="U6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V6" t="n">
         <v>19</v>
@@ -3258,7 +3258,7 @@
         <v>10</v>
       </c>
       <c r="X6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y6" t="n">
         <v>42</v>
@@ -3364,7 +3364,7 @@
         <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>-1</v>
+        <v>13360</v>
       </c>
       <c r="BG6" t="n">
         <v>2</v>
@@ -3424,13 +3424,13 @@
         <v>108</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="CA6" t="n">
         <v>1.97</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.55</v>
+        <v>3.61</v>
       </c>
       <c r="CC6" t="n">
         <v>0</v>
@@ -3481,13 +3481,13 @@
         <v>21</v>
       </c>
       <c r="CS6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="CT6" t="n">
         <v>1</v>
       </c>
       <c r="CU6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CV6" t="n">
         <v>10</v>
@@ -3603,6 +3603,1330 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sweden_Allsvenskan_2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Elfsborg</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>IFK Göteborg</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>46118.5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K7" t="n">
+        <v>7</v>
+      </c>
+      <c r="L7" t="n">
+        <v>13</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>5</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="n">
+        <v>11</v>
+      </c>
+      <c r="U7" t="n">
+        <v>15</v>
+      </c>
+      <c r="V7" t="n">
+        <v>12</v>
+      </c>
+      <c r="W7" t="n">
+        <v>12</v>
+      </c>
+      <c r="X7" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Borås Arena</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Ălgårdsvägen 32, Borås</t>
+        </is>
+      </c>
+      <c r="AC7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>663</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>14344</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>47</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>42</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>84</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>96</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>29</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>7</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>11</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>3</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DP7" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ7" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR7" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS7" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT7" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU7" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV7" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW7" t="inlineStr">
+        <is>
+          <t>3.51</t>
+        </is>
+      </c>
+      <c r="DX7" t="inlineStr">
+        <is>
+          <t>3.16</t>
+        </is>
+      </c>
+      <c r="DY7" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="DZ7" t="inlineStr">
+        <is>
+          <t>3.81</t>
+        </is>
+      </c>
+      <c r="EA7" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EB7" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="EC7" t="inlineStr"/>
+      <c r="ED7" t="inlineStr"/>
+      <c r="EE7" t="inlineStr"/>
+      <c r="EF7" t="inlineStr"/>
+      <c r="EG7" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EH7" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sweden_Allsvenskan_2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Häcken</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Brommapojkarna</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>46118.5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>6</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" t="n">
+        <v>9</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>4</v>
+      </c>
+      <c r="S8" t="n">
+        <v>14</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>17</v>
+      </c>
+      <c r="V8" t="n">
+        <v>7</v>
+      </c>
+      <c r="W8" t="n">
+        <v>13</v>
+      </c>
+      <c r="X8" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>61</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>39</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Bravida Arena</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Inlandsgatan 48, Göteborg</t>
+        </is>
+      </c>
+      <c r="AC8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>4104</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>62</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>37</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>130</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>56</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>26</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>1</v>
+      </c>
+      <c r="DP8" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ8" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR8" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS8" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT8" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU8" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV8" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW8" t="inlineStr">
+        <is>
+          <t>4.67</t>
+        </is>
+      </c>
+      <c r="DX8" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="DY8" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="DZ8" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="EA8" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="EB8" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EC8" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="ED8" t="inlineStr"/>
+      <c r="EE8" t="inlineStr"/>
+      <c r="EF8" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="EG8" t="inlineStr"/>
+      <c r="EH8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sweden_Allsvenskan_2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>GAIS</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Djurgården</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>46118.60416666666</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>10</v>
+      </c>
+      <c r="L9" t="n">
+        <v>12</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>6</v>
+      </c>
+      <c r="R9" t="n">
+        <v>5</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="n">
+        <v>7</v>
+      </c>
+      <c r="U9" t="n">
+        <v>11</v>
+      </c>
+      <c r="V9" t="n">
+        <v>12</v>
+      </c>
+      <c r="W9" t="n">
+        <v>14</v>
+      </c>
+      <c r="X9" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>52</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Gamla Ullevi</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Ullevigatan 5, Göteborg</t>
+        </is>
+      </c>
+      <c r="AC9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>659</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>17165</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>54</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>53</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>118</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>107</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>7</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>3</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>1</v>
+      </c>
+      <c r="DP9" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ9" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR9" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS9" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT9" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU9" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV9" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW9" t="inlineStr">
+        <is>
+          <t>3.62</t>
+        </is>
+      </c>
+      <c r="DX9" t="inlineStr">
+        <is>
+          <t>3.24</t>
+        </is>
+      </c>
+      <c r="DY9" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="DZ9" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="EA9" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EB9" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EC9" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="ED9" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EE9" t="inlineStr">
+        <is>
+          <t>2.89</t>
+        </is>
+      </c>
+      <c r="EF9" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="EG9" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="EH9" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/data/matches/leagues/Sweden_Allsvenskan_2026.xlsx
+++ b/data/matches/leagues/Sweden_Allsvenskan_2026.xlsx
@@ -4347,7 +4347,7 @@
         <v>1</v>
       </c>
       <c r="CU8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CV8" t="n">
         <v>13</v>
@@ -4356,10 +4356,10 @@
         <v>1</v>
       </c>
       <c r="CX8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CY8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="CZ8" t="n">
         <v>0</v>

--- a/data/matches/leagues/Sweden_Allsvenskan_2026.xlsx
+++ b/data/matches/leagues/Sweden_Allsvenskan_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EH9" headerRowCount="1">
-  <autoFilter ref="A1:EH9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EH12" headerRowCount="1">
+  <autoFilter ref="A1:EH12"/>
   <tableColumns count="138">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -576,13 +576,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EH9"/>
+  <dimension ref="A1:EH12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="9.6" customWidth="1" min="2" max="2"/>
     <col width="13.2" customWidth="1" min="3" max="3"/>
-    <col width="13.2" customWidth="1" min="4" max="4"/>
+    <col width="16.8" customWidth="1" min="4" max="4"/>
     <col width="19.2" customWidth="1" min="5" max="5"/>
     <col width="25.2" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
@@ -606,7 +606,7 @@
     <col width="22.8" customWidth="1" min="25" max="25"/>
     <col width="22.8" customWidth="1" min="26" max="26"/>
     <col width="21.6" customWidth="1" min="27" max="27"/>
-    <col width="37.2" customWidth="1" min="28" max="28"/>
+    <col width="46.8" customWidth="1" min="28" max="28"/>
     <col width="21.6" customWidth="1" min="29" max="29"/>
     <col width="21.6" customWidth="1" min="30" max="30"/>
     <col width="18" customWidth="1" min="31" max="31"/>
@@ -3971,7 +3971,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4924,6 +4924,1330 @@
       <c r="EH9" t="inlineStr">
         <is>
           <t>1.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sweden_Allsvenskan_2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Mjällby</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Örgryte</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>46123.54166666666</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>12</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+      <c r="L10" t="n">
+        <v>15</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>4</v>
+      </c>
+      <c r="S10" t="n">
+        <v>18</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>23</v>
+      </c>
+      <c r="V10" t="n">
+        <v>8</v>
+      </c>
+      <c r="W10" t="n">
+        <v>6</v>
+      </c>
+      <c r="X10" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Strandvallen</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Campingvägen 44, Hällevik, Sölvesborg</t>
+        </is>
+      </c>
+      <c r="AC10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>677</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>91</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>24</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>134</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>66</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>18</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>3</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP10" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ10" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR10" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS10" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT10" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU10" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV10" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW10" t="inlineStr">
+        <is>
+          <t>9.34</t>
+        </is>
+      </c>
+      <c r="DX10" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="DY10" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="DZ10" t="inlineStr">
+        <is>
+          <t>2.47</t>
+        </is>
+      </c>
+      <c r="EA10" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="EB10" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EC10" t="inlineStr"/>
+      <c r="ED10" t="inlineStr"/>
+      <c r="EE10" t="inlineStr"/>
+      <c r="EF10" t="inlineStr"/>
+      <c r="EG10" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="EH10" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sweden_Allsvenskan_2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Västerås SK</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Elfsborg</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>46123.54166666666</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>11</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" t="n">
+        <v>3</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>9</v>
+      </c>
+      <c r="V11" t="n">
+        <v>8</v>
+      </c>
+      <c r="W11" t="n">
+        <v>6</v>
+      </c>
+      <c r="X11" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>51</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>49</v>
+      </c>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>8</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>59</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>36</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>97</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>97</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>3</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>3</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP11" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ11" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR11" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS11" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT11" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU11" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV11" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW11" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="DX11" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="DY11" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="DZ11" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
+      </c>
+      <c r="EA11" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EB11" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="EC11" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="ED11" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EE11" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="EF11" t="inlineStr">
+        <is>
+          <t>3.36</t>
+        </is>
+      </c>
+      <c r="EG11" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="EH11" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Sweden_Allsvenskan_2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>IFK Göteborg</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Häcken</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>46123.54166666666</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>9</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" t="n">
+        <v>12</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3</v>
+      </c>
+      <c r="N12" t="n">
+        <v>6</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>7</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7</v>
+      </c>
+      <c r="S12" t="n">
+        <v>12</v>
+      </c>
+      <c r="T12" t="n">
+        <v>5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>19</v>
+      </c>
+      <c r="V12" t="n">
+        <v>12</v>
+      </c>
+      <c r="W12" t="n">
+        <v>8</v>
+      </c>
+      <c r="X12" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>68</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Gamla Ullevi</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>Ullevigatan 5, Göteborg</t>
+        </is>
+      </c>
+      <c r="AC12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>664</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>46</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>26</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>111</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>61</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>3</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP12" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ12" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR12" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS12" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT12" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU12" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV12" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW12" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
+      <c r="DX12" t="inlineStr">
+        <is>
+          <t>3.23</t>
+        </is>
+      </c>
+      <c r="DY12" t="inlineStr">
+        <is>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="DZ12" t="inlineStr">
+        <is>
+          <t>2.77</t>
+        </is>
+      </c>
+      <c r="EA12" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="EB12" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EC12" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="ED12" t="inlineStr"/>
+      <c r="EE12" t="inlineStr"/>
+      <c r="EF12" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="EG12" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="EH12" t="inlineStr">
+        <is>
+          <t>1.46</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Sweden_Allsvenskan_2026.xlsx
+++ b/data/matches/leagues/Sweden_Allsvenskan_2026.xlsx
@@ -34896,21 +34896,9 @@
       <c r="DV78" t="b">
         <v>1</v>
       </c>
-      <c r="DW78" t="inlineStr">
-        <is>
-          <t>2.84</t>
-        </is>
-      </c>
-      <c r="DX78" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="DY78" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
+      <c r="DW78" t="inlineStr"/>
+      <c r="DX78" t="inlineStr"/>
+      <c r="DY78" t="inlineStr"/>
       <c r="DZ78" t="inlineStr">
         <is>
           <t>1.52</t>
@@ -34926,26 +34914,10 @@
           <t>6.12</t>
         </is>
       </c>
-      <c r="EC78" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="ED78" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="EE78" t="inlineStr">
-        <is>
-          <t>3.32</t>
-        </is>
-      </c>
-      <c r="EF78" t="inlineStr">
-        <is>
-          <t>2.59</t>
-        </is>
-      </c>
+      <c r="EC78" t="inlineStr"/>
+      <c r="ED78" t="inlineStr"/>
+      <c r="EE78" t="inlineStr"/>
+      <c r="EF78" t="inlineStr"/>
       <c r="EG78" t="inlineStr">
         <is>
           <t>2.25</t>
@@ -35772,9 +35744,21 @@
       <c r="DV80" t="b">
         <v>1</v>
       </c>
-      <c r="DW80" t="inlineStr"/>
-      <c r="DX80" t="inlineStr"/>
-      <c r="DY80" t="inlineStr"/>
+      <c r="DW80" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="DX80" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="DY80" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
       <c r="DZ80" t="inlineStr">
         <is>
           <t>3.06</t>
@@ -35884,13 +35868,13 @@
         <v>2</v>
       </c>
       <c r="R81" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S81" t="n">
         <v>9</v>
       </c>
       <c r="T81" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U81" t="n">
         <v>11</v>
@@ -36063,10 +36047,10 @@
         <v>1.22</v>
       </c>
       <c r="CA81" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="CB81" t="n">
-        <v>3.24</v>
+        <v>3.17</v>
       </c>
       <c r="CC81" t="n">
         <v>0</v>
@@ -36236,26 +36220,10 @@
           <t>3.38</t>
         </is>
       </c>
-      <c r="EC81" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="ED81" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="EE81" t="inlineStr">
-        <is>
-          <t>2.87</t>
-        </is>
-      </c>
-      <c r="EF81" t="inlineStr">
-        <is>
-          <t>3.06</t>
-        </is>
-      </c>
+      <c r="EC81" t="inlineStr"/>
+      <c r="ED81" t="inlineStr"/>
+      <c r="EE81" t="inlineStr"/>
+      <c r="EF81" t="inlineStr"/>
       <c r="EG81" t="inlineStr">
         <is>
           <t>2.05</t>
